--- a/DeskripsiSektor.xlsx
+++ b/DeskripsiSektor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy---Jawa-Tengah/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68BCB2A9-3034-4403-B0F6-B9866D2064DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{68BCB2A9-3034-4403-B0F6-B9866D2064DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4B04AD3-7911-45AE-97BA-19A88AB55C9C}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{C2824A85-1FF2-4FE4-93CA-E4661EDCEF1F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2824A85-1FF2-4FE4-93CA-E4661EDCEF1F}"/>
   </bookViews>
   <sheets>
     <sheet name="DeskripsiSektor" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>Pd</t>
   </si>
   <si>
-    <t>Pertanian</t>
-  </si>
-  <si>
     <t>Jagung</t>
   </si>
   <si>
@@ -504,6 +501,9 @@
   </si>
   <si>
     <t>SELYTJB</t>
+  </si>
+  <si>
+    <t>Pertanian, Kehutanan, dan Perikanan</t>
   </si>
 </sst>
 </file>
@@ -776,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -796,13 +796,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -849,13 +849,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -875,13 +875,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -901,13 +901,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -927,13 +927,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -953,13 +953,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -979,13 +979,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1005,13 +1005,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1031,13 +1031,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1057,13 +1057,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1109,13 +1109,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1135,13 +1135,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1161,13 +1161,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
         <v>39</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1187,13 +1187,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1213,13 +1213,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
         <v>46</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>47</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1317,13 +1317,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
         <v>53</v>
       </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1369,13 +1369,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
         <v>57</v>
       </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1395,13 +1395,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
         <v>59</v>
       </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
         <v>61</v>
       </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1447,13 +1447,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
         <v>63</v>
       </c>
-      <c r="C28" t="s">
-        <v>64</v>
-      </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1473,13 +1473,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
         <v>65</v>
       </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1499,13 +1499,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
         <v>67</v>
       </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
         <v>69</v>
       </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1551,13 +1551,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
         <v>71</v>
       </c>
-      <c r="C32" t="s">
-        <v>72</v>
-      </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
         <v>73</v>
       </c>
-      <c r="C33" t="s">
-        <v>74</v>
-      </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1603,13 +1603,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
         <v>75</v>
       </c>
-      <c r="C34" t="s">
-        <v>76</v>
-      </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1629,13 +1629,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
         <v>77</v>
       </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s">
         <v>79</v>
       </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
         <v>81</v>
       </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
         <v>83</v>
       </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
         <v>85</v>
       </c>
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1759,13 +1759,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
         <v>87</v>
       </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
         <v>89</v>
       </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1811,13 +1811,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
         <v>91</v>
       </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
         <v>93</v>
       </c>
-      <c r="C43" t="s">
-        <v>94</v>
-      </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1863,13 +1863,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
         <v>95</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>96</v>
-      </c>
-      <c r="D44" t="s">
-        <v>97</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1889,13 +1889,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
         <v>98</v>
       </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1915,13 +1915,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" t="s">
         <v>100</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>101</v>
-      </c>
-      <c r="D46" t="s">
-        <v>102</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1941,13 +1941,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" t="s">
         <v>103</v>
       </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" t="s">
         <v>105</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>107</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
         <v>108</v>
       </c>
-      <c r="C49" t="s">
-        <v>109</v>
-      </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2019,13 +2019,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>111</v>
-      </c>
-      <c r="D50" t="s">
-        <v>112</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" t="s">
         <v>113</v>
       </c>
-      <c r="C51" t="s">
-        <v>114</v>
-      </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2071,13 +2071,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" t="s">
         <v>115</v>
       </c>
-      <c r="C52" t="s">
-        <v>116</v>
-      </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
         <v>117</v>
       </c>
-      <c r="C53" t="s">
-        <v>118</v>
-      </c>
       <c r="D53" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2123,13 +2123,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" t="s">
         <v>119</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>120</v>
-      </c>
-      <c r="D54" t="s">
-        <v>121</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" t="s">
         <v>122</v>
       </c>
-      <c r="C55" t="s">
-        <v>123</v>
-      </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2175,13 +2175,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" t="s">
         <v>124</v>
       </c>
-      <c r="C56" t="s">
-        <v>125</v>
-      </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2201,13 +2201,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s">
         <v>126</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>128</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2227,13 +2227,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" t="s">
         <v>129</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>130</v>
-      </c>
-      <c r="D58" t="s">
-        <v>131</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2253,13 +2253,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" t="s">
         <v>132</v>
       </c>
-      <c r="C59" t="s">
-        <v>133</v>
-      </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" t="s">
         <v>134</v>
       </c>
-      <c r="C60" t="s">
-        <v>135</v>
-      </c>
       <c r="D60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" t="s">
         <v>136</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>137</v>
-      </c>
-      <c r="D61" t="s">
-        <v>138</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2331,13 +2331,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" t="s">
         <v>139</v>
       </c>
-      <c r="C62" t="s">
-        <v>140</v>
-      </c>
       <c r="D62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2357,13 +2357,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" t="s">
         <v>141</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>142</v>
-      </c>
-      <c r="D63" t="s">
-        <v>143</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2383,13 +2383,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" t="s">
         <v>144</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>145</v>
-      </c>
-      <c r="D64" t="s">
-        <v>146</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2409,13 +2409,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
         <v>147</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>148</v>
-      </c>
-      <c r="D65" t="s">
-        <v>149</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2435,13 +2435,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" t="s">
         <v>150</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>151</v>
-      </c>
-      <c r="D66" t="s">
-        <v>152</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2461,13 +2461,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" t="s">
         <v>153</v>
       </c>
-      <c r="C67" t="s">
-        <v>154</v>
-      </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E67">
         <v>0</v>
